--- a/data/GPS/Metricas_GPS19.xlsx
+++ b/data/GPS/Metricas_GPS19.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30508"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C69A3D-4CAE-4F54-B36E-70852322F878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="_ib" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="_synced_data" sheetId="2" r:id="rId6"/>
+    <sheet name="_ib" sheetId="1" r:id="rId1"/>
+    <sheet name="_synced_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -137,25 +146,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="17.0"/>
+      <sz val="17"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -166,38 +176,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -205,7 +220,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -395,26 +410,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="25.25"/>
-    <col customWidth="1" min="3" max="3" width="133.25"/>
+    <col min="2" max="2" width="25.21875" customWidth="1"/>
+    <col min="3" max="3" width="133.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -423,21 +441,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="6" max="7" width="22.25"/>
+    <col min="6" max="7" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -484,9 +503,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B2" s="2">
         <v>161.833</v>
@@ -498,25 +517,25 @@
         <v>19</v>
       </c>
       <c r="E2" s="2">
-        <v>8.473</v>
+        <v>8.4730000000000008</v>
       </c>
       <c r="F2" s="2">
-        <v>1.668</v>
+        <v>1.6679999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>0.207</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="H2" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="J2" s="2">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="K2" s="2">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="L2" s="2">
         <v>5.085</v>
@@ -528,62 +547,62 @@
         <v>28.75</v>
       </c>
       <c r="O2" s="2">
-        <v>1666.831</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>1666.8309999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B3" s="2">
-        <v>153.567</v>
+        <v>153.56700000000001</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2">
-        <v>5.345</v>
+        <v>5.3449999999999998</v>
       </c>
       <c r="F3" s="2">
-        <v>0.619</v>
+        <v>0.61899999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="H3" s="2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="I3" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="J3" s="2">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="L3" s="2">
-        <v>5.467</v>
+        <v>5.4669999999999996</v>
       </c>
       <c r="M3" s="2">
-        <v>-5.743</v>
+        <v>-5.7430000000000003</v>
       </c>
       <c r="N3" s="2">
         <v>31.064</v>
       </c>
       <c r="O3" s="2">
-        <v>1017.267</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>1017.2670000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B4" s="2">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
@@ -592,7 +611,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="2">
-        <v>6.281</v>
+        <v>6.2809999999999997</v>
       </c>
       <c r="F4" s="2">
         <v>1.22</v>
@@ -601,36 +620,36 @@
         <v>0.108</v>
       </c>
       <c r="H4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J4" s="2">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="K4" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L4" s="2">
-        <v>5.013</v>
+        <v>5.0129999999999999</v>
       </c>
       <c r="M4" s="2">
-        <v>-4.719</v>
+        <v>-4.7190000000000003</v>
       </c>
       <c r="N4" s="2">
-        <v>28.789</v>
+        <v>28.789000000000001</v>
       </c>
       <c r="O4" s="2">
-        <v>1153.552</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>1153.5519999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B5" s="2">
-        <v>154.2</v>
+        <v>154.19999999999999</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>23</v>
@@ -642,42 +661,42 @@
         <v>11.875</v>
       </c>
       <c r="F5" s="2">
-        <v>1.064</v>
+        <v>1.0640000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>0.176</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="H5" s="2">
-        <v>0.024</v>
+        <v>2.4E-2</v>
       </c>
       <c r="I5" s="2">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="J5" s="2">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="K5" s="2">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="L5" s="2">
-        <v>5.034</v>
+        <v>5.0339999999999998</v>
       </c>
       <c r="M5" s="2">
-        <v>-5.509</v>
+        <v>-5.5090000000000003</v>
       </c>
       <c r="N5" s="2">
-        <v>30.784</v>
+        <v>30.783999999999999</v>
       </c>
       <c r="O5" s="2">
         <v>2451.712</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B6" s="2">
-        <v>153.867</v>
+        <v>153.86699999999999</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>25</v>
@@ -686,42 +705,42 @@
         <v>26</v>
       </c>
       <c r="E6" s="2">
-        <v>9.629</v>
+        <v>9.6289999999999996</v>
       </c>
       <c r="F6" s="2">
-        <v>0.685</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="G6" s="2">
-        <v>0.026</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="H6" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="K6" s="2">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="L6" s="2">
-        <v>5.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M6" s="2">
-        <v>-5.632</v>
+        <v>-5.6319999999999997</v>
       </c>
       <c r="N6" s="2">
-        <v>27.745</v>
+        <v>27.745000000000001</v>
       </c>
       <c r="O6" s="2">
         <v>1740.579</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B7" s="2">
         <v>173.2</v>
@@ -736,7 +755,7 @@
         <v>5.944</v>
       </c>
       <c r="F7" s="2">
-        <v>1.015</v>
+        <v>1.0149999999999999</v>
       </c>
       <c r="G7" s="2">
         <v>0.127</v>
@@ -745,30 +764,30 @@
         <v>0.06</v>
       </c>
       <c r="I7" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="J7" s="2">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="K7" s="2">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="L7" s="2">
-        <v>5.567</v>
+        <v>5.5670000000000002</v>
       </c>
       <c r="M7" s="2">
-        <v>-4.834</v>
+        <v>-4.8339999999999996</v>
       </c>
       <c r="N7" s="2">
-        <v>32.159</v>
+        <v>32.158999999999999</v>
       </c>
       <c r="O7" s="2">
-        <v>906.388</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>906.38800000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B8" s="2">
         <v>150.65</v>
@@ -780,31 +799,31 @@
         <v>24</v>
       </c>
       <c r="E8" s="2">
-        <v>9.853</v>
+        <v>9.8529999999999998</v>
       </c>
       <c r="F8" s="2">
         <v>0.753</v>
       </c>
       <c r="G8" s="2">
-        <v>0.082</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="H8" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="K8" s="2">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="L8" s="2">
-        <v>5.019</v>
+        <v>5.0190000000000001</v>
       </c>
       <c r="M8" s="2">
-        <v>-5.895</v>
+        <v>-5.8949999999999996</v>
       </c>
       <c r="N8" s="2">
         <v>28.163</v>
@@ -813,12 +832,12 @@
         <v>2093.002</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B9" s="2">
-        <v>161.467</v>
+        <v>161.46700000000001</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -833,36 +852,36 @@
         <v>1.371</v>
       </c>
       <c r="G9" s="2">
-        <v>0.402</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="H9" s="2">
         <v>0.107</v>
       </c>
       <c r="I9" s="2">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="J9" s="2">
-        <v>62.0</v>
+        <v>62</v>
       </c>
       <c r="K9" s="2">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="L9" s="2">
-        <v>5.469</v>
+        <v>5.4690000000000003</v>
       </c>
       <c r="M9" s="2">
-        <v>-6.844</v>
+        <v>-6.8440000000000003</v>
       </c>
       <c r="N9" s="2">
-        <v>33.178</v>
+        <v>33.177999999999997</v>
       </c>
       <c r="O9" s="2">
-        <v>444.313</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>444.31299999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B10" s="2">
         <v>150.083</v>
@@ -877,39 +896,39 @@
         <v>7.819</v>
       </c>
       <c r="F10" s="2">
-        <v>0.798</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="G10" s="2">
-        <v>0.013</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="H10" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J10" s="2">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="K10" s="2">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="L10" s="2">
-        <v>4.919</v>
+        <v>4.9189999999999996</v>
       </c>
       <c r="M10" s="2">
-        <v>-6.033</v>
+        <v>-6.0330000000000004</v>
       </c>
       <c r="N10" s="2">
-        <v>27.299</v>
+        <v>27.298999999999999</v>
       </c>
       <c r="O10" s="2">
-        <v>1549.901</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>1549.9010000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B11" s="2">
         <v>150.267</v>
@@ -924,42 +943,42 @@
         <v>13.606</v>
       </c>
       <c r="F11" s="2">
-        <v>1.727</v>
+        <v>1.7270000000000001</v>
       </c>
       <c r="G11" s="2">
         <v>0.191</v>
       </c>
       <c r="H11" s="2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="I11" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="J11" s="2">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="K11" s="2">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="L11" s="2">
-        <v>4.775</v>
+        <v>4.7750000000000004</v>
       </c>
       <c r="M11" s="2">
         <v>-6.282</v>
       </c>
       <c r="N11" s="2">
-        <v>30.859</v>
+        <v>30.859000000000002</v>
       </c>
       <c r="O11" s="2">
-        <v>619.884</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>619.88400000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B12" s="2">
-        <v>150.867</v>
+        <v>150.86699999999999</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>34</v>
@@ -971,42 +990,42 @@
         <v>12.525</v>
       </c>
       <c r="F12" s="2">
-        <v>1.124</v>
+        <v>1.1240000000000001</v>
       </c>
       <c r="G12" s="2">
         <v>0.153</v>
       </c>
       <c r="H12" s="2">
-        <v>0.051</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="I12" s="2">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="J12" s="2">
-        <v>66.0</v>
+        <v>66</v>
       </c>
       <c r="K12" s="2">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="L12" s="2">
-        <v>4.881</v>
+        <v>4.8810000000000002</v>
       </c>
       <c r="M12" s="2">
-        <v>-6.893</v>
+        <v>-6.8929999999999998</v>
       </c>
       <c r="N12" s="2">
-        <v>32.483</v>
+        <v>32.482999999999997</v>
       </c>
       <c r="O12" s="2">
-        <v>3018.591</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>3018.5909999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B13" s="2">
-        <v>159.367</v>
+        <v>159.36699999999999</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>35</v>
@@ -1015,45 +1034,45 @@
         <v>19</v>
       </c>
       <c r="E13" s="2">
-        <v>11.473</v>
+        <v>11.473000000000001</v>
       </c>
       <c r="F13" s="2">
-        <v>0.981</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="G13" s="2">
-        <v>0.065</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="H13" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="J13" s="2">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="K13" s="2">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="L13" s="2">
-        <v>5.404</v>
+        <v>5.4039999999999999</v>
       </c>
       <c r="M13" s="2">
-        <v>-6.033</v>
+        <v>-6.0330000000000004</v>
       </c>
       <c r="N13" s="2">
-        <v>28.652</v>
+        <v>28.652000000000001</v>
       </c>
       <c r="O13" s="2">
         <v>2075.143</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B14" s="2">
-        <v>153.067</v>
+        <v>153.06700000000001</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>36</v>
@@ -1062,42 +1081,42 @@
         <v>33</v>
       </c>
       <c r="E14" s="2">
-        <v>7.953</v>
+        <v>7.9530000000000003</v>
       </c>
       <c r="F14" s="2">
-        <v>0.784</v>
+        <v>0.78400000000000003</v>
       </c>
       <c r="G14" s="2">
-        <v>0.094</v>
+        <v>9.4E-2</v>
       </c>
       <c r="H14" s="2">
-        <v>0.005</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I14" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J14" s="2">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="K14" s="2">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="L14" s="2">
         <v>4.694</v>
       </c>
       <c r="M14" s="2">
-        <v>-5.876</v>
+        <v>-5.8760000000000003</v>
       </c>
       <c r="N14" s="2">
-        <v>29.066</v>
+        <v>29.065999999999999</v>
       </c>
       <c r="O14" s="2">
         <v>1745.518</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B15" s="2">
         <v>115.267</v>
@@ -1109,42 +1128,42 @@
         <v>33</v>
       </c>
       <c r="E15" s="2">
-        <v>9.112</v>
+        <v>9.1120000000000001</v>
       </c>
       <c r="F15" s="2">
-        <v>0.934</v>
+        <v>0.93400000000000005</v>
       </c>
       <c r="G15" s="2">
-        <v>0.065</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="H15" s="2">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="I15" s="2">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="J15" s="2">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="K15" s="2">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="L15" s="2">
-        <v>5.143</v>
+        <v>5.1429999999999998</v>
       </c>
       <c r="M15" s="2">
-        <v>-5.451</v>
+        <v>-5.4509999999999996</v>
       </c>
       <c r="N15" s="2">
-        <v>28.886</v>
+        <v>28.885999999999999</v>
       </c>
       <c r="O15" s="2">
-        <v>2177.744</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>2177.7440000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B16" s="2">
         <v>147.75</v>
@@ -1156,10 +1175,10 @@
         <v>30</v>
       </c>
       <c r="E16" s="2">
-        <v>7.594</v>
+        <v>7.5940000000000003</v>
       </c>
       <c r="F16" s="2">
-        <v>0.883</v>
+        <v>0.88300000000000001</v>
       </c>
       <c r="G16" s="2">
         <v>0.13</v>
@@ -1168,33 +1187,33 @@
         <v>0.02</v>
       </c>
       <c r="I16" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="J16" s="2">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="K16" s="2">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="L16" s="2">
-        <v>4.368</v>
+        <v>4.3680000000000003</v>
       </c>
       <c r="M16" s="2">
-        <v>-5.998</v>
+        <v>-5.9980000000000002</v>
       </c>
       <c r="N16" s="2">
-        <v>29.909</v>
+        <v>29.908999999999999</v>
       </c>
       <c r="O16" s="2">
-        <v>1332.129</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>1332.1289999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>46277.0</v>
+        <v>46277</v>
       </c>
       <c r="B17" s="2">
-        <v>86.683</v>
+        <v>86.683000000000007</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>39</v>
@@ -1209,19 +1228,19 @@
         <v>0.41</v>
       </c>
       <c r="G17" s="2">
-        <v>0.032</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H17" s="2">
-        <v>0.002</v>
+        <v>2E-3</v>
       </c>
       <c r="I17" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J17" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="K17" s="2">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="L17" s="2">
         <v>5.202</v>
@@ -1230,13 +1249,13 @@
         <v>-5.242</v>
       </c>
       <c r="N17" s="2">
-        <v>29.711</v>
+        <v>29.710999999999999</v>
       </c>
       <c r="O17" s="2">
-        <v>797.103</v>
+        <v>797.10299999999995</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>